--- a/erp-server/erp-server-wms/src/main/resources/excel/packingExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packingExport.xlsx
@@ -11,7 +11,20 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -42,7 +55,7 @@
     <t>{.boxSize}</t>
   </si>
   <si>
-    <t>{.packageWeighte}</t>
+    <t>{.packageWeight}</t>
   </si>
   <si>
     <t>{.boxDesc}</t>
@@ -51,7 +64,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1056,9 +1069,9 @@
     <col min="7" max="7" width="6" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="9" max="9" width="15.125" customWidth="1"/>
-    <col min="10" max="10" width="5.25" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="6.25" customWidth="1"/>
+    <col min="11" max="11" width="14.75" customWidth="1"/>
+    <col min="12" max="12" width="16.875" customWidth="1"/>
     <col min="13" max="13" width="78.5" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="36.375" customWidth="1"/>
